--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -702,7 +702,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -721,7 +721,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -740,7 +740,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -778,7 +778,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -794,6 +794,120 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -702,7 +702,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -721,7 +721,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -740,7 +740,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -778,7 +778,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -794,6 +794,82 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -456,35 +456,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -507,7 +502,6 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -526,12 +520,11 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -545,12 +538,11 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -564,12 +556,11 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -583,12 +574,11 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -602,12 +592,11 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -621,12 +610,11 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -640,7 +628,6 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -659,7 +646,6 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -678,7 +664,6 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -697,7 +682,6 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -716,7 +700,6 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -735,7 +718,6 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -754,12 +736,11 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -773,12 +754,11 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -792,12 +772,11 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -811,12 +790,11 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -830,12 +808,11 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -849,12 +826,11 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -868,7 +844,6 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -557,294 +557,6 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>GrNwFMem</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>8x0Cb1B6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -456,30 +456,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -488,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -502,11 +507,12 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -520,11 +526,12 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -538,11 +545,12 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -556,6 +564,235 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -456,35 +456,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -507,7 +502,6 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -526,7 +520,6 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -545,7 +538,6 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -564,7 +556,6 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -583,7 +574,6 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -602,7 +592,6 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -621,7 +610,6 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -640,7 +628,6 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -659,7 +646,6 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -678,7 +664,6 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -697,7 +682,6 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -716,7 +700,6 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -735,7 +718,6 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -754,7 +736,6 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -773,7 +754,6 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -792,7 +772,6 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -701,78 +701,6 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,42 +665,6 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,42 +629,6 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,78 +557,6 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -557,6 +557,114 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -632,7 +632,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -665,6 +665,186 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>xIieTySH</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -611,240 +611,6 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zTBIR3ZF</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>SQjcKLRk</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>v1I9TP43</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>n7VN5MCd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -611,6 +611,240 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -614,7 +614,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -629,222 +629,6 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WvDUsysB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>pOEMqcCb</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>A50vXJSh</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>O8QDoJsn</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Yqo4RFdU</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,59 +436,34 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>mean_last_360_matches_mean_rat_player_start_home_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>mean_last_360_matches_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_start</t>
+          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -497,16 +472,11 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -515,16 +485,11 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -533,16 +498,11 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -551,16 +511,11 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -569,16 +524,11 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -587,16 +537,11 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -605,11 +550,188 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -473,266 +473,6 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -577,162 +577,6 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,146 +436,85 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_360_matches_mean_rat_player_start_home_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_360_matches_mean_rat_player_start_away_against</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
@@ -453,68 +458,146 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -482,7 +482,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -506,7 +506,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -590,7 +590,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -599,6 +599,30 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,29 +436,84 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start_against</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -466,11 +521,22 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -478,11 +544,22 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -490,11 +567,22 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -502,11 +590,22 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -514,11 +613,22 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -526,11 +636,22 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -538,11 +659,22 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -550,11 +682,22 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -562,11 +705,22 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -574,11 +728,22 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -586,11 +751,22 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -598,11 +774,22 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -610,11 +797,22 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -622,6 +820,224 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -559,7 +559,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -582,7 +582,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -605,7 +605,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -628,7 +628,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -651,7 +651,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -674,7 +674,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -697,7 +697,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -720,7 +720,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -743,7 +743,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -766,7 +766,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -789,7 +789,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -812,7 +812,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -835,7 +835,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -858,7 +858,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -881,7 +881,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -904,7 +904,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -927,7 +927,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -950,7 +950,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -973,7 +973,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -996,7 +996,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1039,6 +1039,121 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_mean_rat_player_start_against</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -466,54 +466,14 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EssDGebM</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,19 +484,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rcXrBZLq</t>
+          <t>p2kdKwac</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -547,19 +499,11 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Y96v2dqT</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -570,19 +514,11 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0b5fTYsS</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -593,19 +529,11 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IFm4IHT9</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -616,19 +544,11 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -639,19 +559,11 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -662,19 +574,11 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -685,19 +589,11 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -708,19 +604,11 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -731,19 +619,11 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -754,19 +634,11 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -777,19 +649,11 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -800,19 +664,11 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -823,19 +679,11 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -846,19 +694,11 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -869,19 +709,11 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -892,19 +724,11 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -915,19 +739,11 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -938,19 +754,11 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -961,19 +769,11 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -984,19 +784,11 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1007,19 +799,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1030,19 +814,11 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1053,19 +829,11 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1076,19 +844,11 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1099,19 +859,11 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1122,19 +874,11 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1145,14 +889,36 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Sp7nVfDF</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p2kdKwac</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EssDGebM</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rcXrBZLq</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y96v2dqT</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0b5fTYsS</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -560,366 +560,6 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8f71RSPs</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UuMqRJVb</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>bLD0NyVN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>I5fXHFho</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>0lpzB7u1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>GMBD7YY8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>dGwq9oAD</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>AJ5eIkmR</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>8Kjh0jRr</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>2g2mKBIE</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>SznSCTAl</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Cl5M5C3L</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>EXLhbUee</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>rXmhxCKr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>vJXfdXBE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>jqCRLjz2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>v5hMsYdL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>WvkEqfS8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>b7pTwPem</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -560,6 +560,366 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8f71RSPs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>I5fXHFho</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -593,7 +593,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -605,321 +605,6 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>p2kdKwac</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Sp7nVfDF</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>EssDGebM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Y96v2dqT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rcXrBZLq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>0b5fTYsS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>8f71RSPs</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>UuMqRJVb</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>bLD0NyVN</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>I5fXHFho</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,174 +436,326 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_start</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.07493564310501995</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>rXmhxCKr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -458,17 +458,21 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.08993819205826524</v>
+      </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>vJXfdXBE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -478,7 +482,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>v5hMsYdL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -488,7 +492,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>WvkEqfS8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -498,7 +502,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>b7pTwPem</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -508,7 +512,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>CCu9YTJ7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -518,7 +522,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>Gpn0zjke</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -528,7 +532,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>pOryx3Qa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -538,224 +542,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.07493564310501995</v>
-      </c>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rXmhxCKr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>vJXfdXBE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.07493564310501995</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>p2kdKwac</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.07493564310501995</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Sp7nVfDF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>EssDGebM</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rcXrBZLq</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Y96v2dqT</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>0b5fTYsS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -458,21 +458,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.08993819205826524</v>
-      </c>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -482,7 +478,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -492,7 +488,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -502,7 +498,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -512,7 +508,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -522,7 +518,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -532,7 +528,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -542,11 +538,15 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1227694362986405</v>
+      </c>
       <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,118 +436,172 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_wage_player_start</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>z7KrCz8T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.1227694362986405</v>
-      </c>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
